--- a/task130/target/dps_lot2_lot3_price_schedule.xlsx
+++ b/task130/target/dps_lot2_lot3_price_schedule.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rates per unit, excluding VAT (not chargeable). 2027/28 rates apply to units starting on or after 1 April 2027 and to every unit from that date; uplift by September 2026 CPI, 3.8 per cent.</t>
+          <t>Rates per unit, excluding VAT (not chargeable). 2027/28 rates apply to units starting on or after 1 April 2027 and to every unit from that date; uplift by August 2026 CPI, 3.8 per cent.</t>
         </is>
       </c>
     </row>
